--- a/src/dataset/outputs/schoolshooters.xlsx
+++ b/src/dataset/outputs/schoolshooters.xlsx
@@ -3070,7 +3070,7 @@
   <dimension ref="A1:D872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="100.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" customWidth="1"/>
